--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_14_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_14_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0590569-512B-4527-81A4-B1BA4A6180CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5381A9-ADE3-4DD1-9D2F-E553B447F8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,25 +55,61 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT KEI 31 Jul 2025 3600 CE</t>
-  </si>
-  <si>
-    <t>14-07-2025</t>
-  </si>
-  <si>
-    <t>OPT TATAELXSI 31 Jul 2025 6300 CE</t>
-  </si>
-  <si>
-    <t>15-07-2025</t>
-  </si>
-  <si>
-    <t>OPT SUNPHARMA 31 Jul 2025 1700 CE</t>
-  </si>
-  <si>
-    <t>OPT DALBHARAT 31 Jul 2025 2220 CE</t>
-  </si>
-  <si>
-    <t>18-07-2025</t>
+    <t>OPT ADANIENT 28 Aug 2025 2350 CE</t>
+  </si>
+  <si>
+    <t>19-08-2025</t>
+  </si>
+  <si>
+    <t>OPT HINDUNILVR 28 Aug 2025 2600 CE</t>
+  </si>
+  <si>
+    <t>20-08-2025</t>
+  </si>
+  <si>
+    <t>OPT PGEL 28 Aug 2025 560 CE</t>
+  </si>
+  <si>
+    <t>OPT KAYNES 28 Aug 2025 6200 PE</t>
+  </si>
+  <si>
+    <t>OPT KEI 28 Aug 2025 4000 CE</t>
+  </si>
+  <si>
+    <t>OPT TCS 28 Aug 2025 3100 CE</t>
+  </si>
+  <si>
+    <t>21-08-2025</t>
+  </si>
+  <si>
+    <t>OPT MANKIND 28 Aug 2025 2500 CE</t>
+  </si>
+  <si>
+    <t>OPT TATAELXSI 28 Aug 2025 5700 PE</t>
+  </si>
+  <si>
+    <t>OPT ALKEM 28 Aug 2025 5400 CE</t>
+  </si>
+  <si>
+    <t>OPT HAL 28 Aug 2025 4500 CE</t>
+  </si>
+  <si>
+    <t>OPT TATAELXSI 28 Aug 2025 5600 CE</t>
+  </si>
+  <si>
+    <t>22-08-2025</t>
+  </si>
+  <si>
+    <t>OPT LAURUSLABS 28 Aug 2025 890 PE</t>
+  </si>
+  <si>
+    <t>OPT TIINDIA 28 Aug 2025 3200 CE</t>
+  </si>
+  <si>
+    <t>OPT LAURUSLABS 28 Aug 2025 890 CE</t>
+  </si>
+  <si>
+    <t>OPT INDHOTEL 28 Aug 2025 800 PE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -426,10 +462,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -445,10 +481,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -457,10 +493,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -483,190 +519,707 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>157</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45852</v>
+        <v>45888</v>
       </c>
       <c r="D2">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="E2">
-        <v>178.9</v>
+        <v>54</v>
       </c>
       <c r="F2">
-        <v>31307.5</v>
+        <v>16200</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="I2">
-        <v>171.95</v>
+        <v>58</v>
       </c>
       <c r="J2">
-        <v>30091.25</v>
+        <v>17400</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>-1216.25</v>
+        <v>1200</v>
       </c>
       <c r="M2">
-        <v>104.02</v>
+        <v>78.319999999999993</v>
       </c>
       <c r="N2">
-        <v>-1320.27</v>
+        <v>1121.68</v>
       </c>
       <c r="O2">
-        <v>1216.25</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45853</v>
+        <v>45889</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E3">
-        <v>178.53</v>
+        <v>51.5</v>
       </c>
       <c r="F3">
-        <v>35705</v>
+        <v>15450</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I3">
-        <v>194.5</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>38900</v>
+        <v>18000</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>3195</v>
+        <v>2550</v>
       </c>
       <c r="M3">
-        <v>141.35</v>
+        <v>79.72</v>
       </c>
       <c r="N3">
-        <v>3053.65</v>
+        <v>2470.2800000000002</v>
       </c>
       <c r="O3">
-        <v>3195</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>45853</v>
+        <v>45889</v>
       </c>
       <c r="D4">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E4">
-        <v>27.3</v>
+        <v>24.3</v>
       </c>
       <c r="F4">
-        <v>9555</v>
+        <v>17010</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H4">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="I4">
-        <v>21.5</v>
+        <v>22.45</v>
       </c>
       <c r="J4">
-        <v>7525</v>
+        <v>15715</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>-2030</v>
+        <v>-1295</v>
       </c>
       <c r="M4">
-        <v>62.2</v>
+        <v>77.19</v>
       </c>
       <c r="N4">
-        <v>-2092.1999999999998</v>
+        <v>-1372.19</v>
       </c>
       <c r="O4">
-        <v>2030</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>45856</v>
+        <v>45889</v>
       </c>
       <c r="D5">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="E5">
-        <v>61.95</v>
+        <v>113</v>
       </c>
       <c r="F5">
-        <v>20133.75</v>
+        <v>11300</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>10000</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>-1300</v>
+      </c>
+      <c r="M5">
+        <v>66.5</v>
+      </c>
+      <c r="N5">
+        <v>-1366.5</v>
+      </c>
+      <c r="O5">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>158</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="H5">
-        <v>325</v>
-      </c>
-      <c r="I5">
-        <v>66.5</v>
-      </c>
-      <c r="J5">
-        <v>21612.5</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>1478.75</v>
-      </c>
-      <c r="M5">
-        <v>87.75</v>
-      </c>
-      <c r="N5">
-        <v>1391</v>
-      </c>
-      <c r="O5">
-        <v>1478.75</v>
+      <c r="C6" s="1">
+        <v>45889</v>
+      </c>
+      <c r="D6">
+        <v>175</v>
+      </c>
+      <c r="E6">
+        <v>111</v>
+      </c>
+      <c r="F6">
+        <v>19425</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>175</v>
+      </c>
+      <c r="I6">
+        <v>105</v>
+      </c>
+      <c r="J6">
+        <v>18375</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>-1050</v>
+      </c>
+      <c r="M6">
+        <v>82.07</v>
+      </c>
+      <c r="N6">
+        <v>-1132.07</v>
+      </c>
+      <c r="O6">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>275</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45890</v>
+      </c>
+      <c r="D7">
+        <v>175</v>
+      </c>
+      <c r="E7">
+        <v>32.4</v>
+      </c>
+      <c r="F7">
+        <v>5670</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>175</v>
+      </c>
+      <c r="I7">
+        <v>36.4</v>
+      </c>
+      <c r="J7">
+        <v>6370</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>700</v>
+      </c>
+      <c r="M7">
+        <v>58.8</v>
+      </c>
+      <c r="N7">
+        <v>641.20000000000005</v>
+      </c>
+      <c r="O7">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>172</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45890</v>
+      </c>
+      <c r="D8">
+        <v>225</v>
+      </c>
+      <c r="E8">
+        <v>97.5</v>
+      </c>
+      <c r="F8">
+        <v>21937.5</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>225</v>
+      </c>
+      <c r="I8">
+        <v>104.15</v>
+      </c>
+      <c r="J8">
+        <v>23433.75</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>1496.25</v>
+      </c>
+      <c r="M8">
+        <v>90.09</v>
+      </c>
+      <c r="N8">
+        <v>1406.16</v>
+      </c>
+      <c r="O8">
+        <v>1496.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>263</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45890</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>85</v>
+      </c>
+      <c r="F9">
+        <v>8500</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>87</v>
+      </c>
+      <c r="J9">
+        <v>8700</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>200</v>
+      </c>
+      <c r="M9">
+        <v>63.39</v>
+      </c>
+      <c r="N9">
+        <v>136.61000000000001</v>
+      </c>
+      <c r="O9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45890</v>
+      </c>
+      <c r="D10">
+        <v>125</v>
+      </c>
+      <c r="E10">
+        <v>96.7</v>
+      </c>
+      <c r="F10">
+        <v>12087.5</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10">
+        <v>125</v>
+      </c>
+      <c r="I10">
+        <v>99.45</v>
+      </c>
+      <c r="J10">
+        <v>12431.25</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>343.75</v>
+      </c>
+      <c r="M10">
+        <v>70.3</v>
+      </c>
+      <c r="N10">
+        <v>273.45</v>
+      </c>
+      <c r="O10">
+        <v>343.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45890</v>
+      </c>
+      <c r="D11">
+        <v>150</v>
+      </c>
+      <c r="E11">
+        <v>86.75</v>
+      </c>
+      <c r="F11">
+        <v>13012.5</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11">
+        <v>150</v>
+      </c>
+      <c r="I11">
+        <v>76.650000000000006</v>
+      </c>
+      <c r="J11">
+        <v>11497.5</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>-1515</v>
+      </c>
+      <c r="M11">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="N11">
+        <v>-1584.4</v>
+      </c>
+      <c r="O11">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>261</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45891</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>68</v>
+      </c>
+      <c r="F12">
+        <v>6800</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <v>61.9</v>
+      </c>
+      <c r="J12">
+        <v>6190</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>-610</v>
+      </c>
+      <c r="M12">
+        <v>59.05</v>
+      </c>
+      <c r="N12">
+        <v>-669.05</v>
+      </c>
+      <c r="O12">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>164</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45891</v>
+      </c>
+      <c r="D13">
+        <v>1700</v>
+      </c>
+      <c r="E13">
+        <v>14.8</v>
+      </c>
+      <c r="F13">
+        <v>25160</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>1700</v>
+      </c>
+      <c r="I13">
+        <v>13.1</v>
+      </c>
+      <c r="J13">
+        <v>22270</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>-2890</v>
+      </c>
+      <c r="M13">
+        <v>89.45</v>
+      </c>
+      <c r="N13">
+        <v>-2979.45</v>
+      </c>
+      <c r="O13">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>277</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45891</v>
+      </c>
+      <c r="D14">
+        <v>200</v>
+      </c>
+      <c r="E14">
+        <v>48</v>
+      </c>
+      <c r="F14">
+        <v>9600</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <v>200</v>
+      </c>
+      <c r="I14">
+        <v>36.5</v>
+      </c>
+      <c r="J14">
+        <v>7300</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>-2300</v>
+      </c>
+      <c r="M14">
+        <v>61.9</v>
+      </c>
+      <c r="N14">
+        <v>-2361.9</v>
+      </c>
+      <c r="O14">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>162</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45891</v>
+      </c>
+      <c r="D15">
+        <v>1700</v>
+      </c>
+      <c r="E15">
+        <v>11.4</v>
+      </c>
+      <c r="F15">
+        <v>19380</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15">
+        <v>1700</v>
+      </c>
+      <c r="I15">
+        <v>11.6</v>
+      </c>
+      <c r="J15">
+        <v>19720</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>340</v>
+      </c>
+      <c r="M15">
+        <v>83.94</v>
+      </c>
+      <c r="N15">
+        <v>256.06</v>
+      </c>
+      <c r="O15">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45891</v>
+      </c>
+      <c r="D16">
+        <v>1000</v>
+      </c>
+      <c r="E16">
+        <v>13.65</v>
+      </c>
+      <c r="F16">
+        <v>13650</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16">
+        <v>1000</v>
+      </c>
+      <c r="I16">
+        <v>14</v>
+      </c>
+      <c r="J16">
+        <v>14000</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>350</v>
+      </c>
+      <c r="M16">
+        <v>73.239999999999995</v>
+      </c>
+      <c r="N16">
+        <v>276.76</v>
+      </c>
+      <c r="O16">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
